--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450306</v>
+        <v>450343</v>
       </c>
       <c r="R16" t="n">
-        <v>6437773</v>
+        <v>6438074</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -1920,7 +1920,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119721578</v>
+        <v>119721010</v>
       </c>
       <c r="B12" t="n">
         <v>91840</v>
@@ -1954,9 +1954,6 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>V bärtebo, Vg</t>
@@ -1998,7 +1995,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2008,7 +2005,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,7 +2014,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,17 +2025,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Louise Säf</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119720265</v>
+        <v>119720043</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,25 +2044,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2079,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450347</v>
+        <v>450402</v>
       </c>
       <c r="R13" t="n">
-        <v>6437947</v>
+        <v>6437806</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2114,7 +2110,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2124,7 +2120,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119720043</v>
+        <v>119720265</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,25 +2160,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2191,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450402</v>
+        <v>450347</v>
       </c>
       <c r="R14" t="n">
-        <v>6437806</v>
+        <v>6437947</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2230,7 +2226,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2240,7 +2236,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -1804,10 +1804,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119721066</v>
+        <v>119721010</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1816,31 +1816,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>V bärtebo, Vg</t>
@@ -1882,7 +1879,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1892,7 +1889,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1901,7 +1898,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1913,17 +1909,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Louise Säf</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119721010</v>
+        <v>119721066</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1932,28 +1928,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>V bärtebo, Vg</t>
@@ -1995,7 +1994,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2005,7 +2004,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,6 +2013,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2025,17 +2025,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Anders Hildingsson, Louise Säf</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119720043</v>
+        <v>119720265</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,25 +2044,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450402</v>
+        <v>450347</v>
       </c>
       <c r="R13" t="n">
-        <v>6437806</v>
+        <v>6437947</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119720265</v>
+        <v>119720296</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2187,14 +2187,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>V bärtebo, V bärtebo, Vg</t>
+          <t>V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450347</v>
+        <v>450306</v>
       </c>
       <c r="R14" t="n">
-        <v>6437947</v>
+        <v>6437773</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119720296</v>
+        <v>119720043</v>
       </c>
       <c r="B15" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,25 +2276,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2303,14 +2303,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>V bärtebo, Vg</t>
+          <t>V bärtebo, V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450306</v>
+        <v>450402</v>
       </c>
       <c r="R15" t="n">
-        <v>6437773</v>
+        <v>6437806</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -1804,7 +1804,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119721010</v>
+        <v>119721578</v>
       </c>
       <c r="B11" t="n">
         <v>91840</v>
@@ -1838,6 +1838,9 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>V bärtebo, Vg</t>
@@ -1879,7 +1882,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1889,7 +1892,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,6 +1901,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1909,14 +1913,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Anders Hildingsson, Louise Säf</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119721066</v>
+        <v>119720265</v>
       </c>
       <c r="B12" t="n">
         <v>91856</v>
@@ -1955,14 +1959,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>V bärtebo, Vg</t>
+          <t>V bärtebo, V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450306</v>
+        <v>450347</v>
       </c>
       <c r="R12" t="n">
-        <v>6437773</v>
+        <v>6437947</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1994,7 +1998,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2004,7 +2008,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,7 +2036,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119720265</v>
+        <v>119721569</v>
       </c>
       <c r="B13" t="n">
         <v>91856</v>
@@ -2071,14 +2075,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>V bärtebo, V bärtebo, Vg</t>
+          <t>V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450347</v>
+        <v>450306</v>
       </c>
       <c r="R13" t="n">
-        <v>6437947</v>
+        <v>6437773</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2110,7 +2114,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2120,7 +2124,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119720296</v>
+        <v>119720043</v>
       </c>
       <c r="B14" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,25 +2164,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2187,14 +2191,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>V bärtebo, Vg</t>
+          <t>V bärtebo, V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450306</v>
+        <v>450402</v>
       </c>
       <c r="R14" t="n">
-        <v>6437773</v>
+        <v>6437806</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2226,7 +2230,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2236,7 +2240,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,10 +2268,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119720043</v>
+        <v>119720296</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,25 +2280,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2303,14 +2307,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>V bärtebo, V bärtebo, Vg</t>
+          <t>V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450402</v>
+        <v>450306</v>
       </c>
       <c r="R15" t="n">
-        <v>6437806</v>
+        <v>6437773</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2342,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2352,7 +2356,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -1804,10 +1804,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119721578</v>
+        <v>119720043</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1843,14 +1843,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>V bärtebo, Vg</t>
+          <t>V bärtebo, V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450306</v>
+        <v>450402</v>
       </c>
       <c r="R11" t="n">
-        <v>6437773</v>
+        <v>6437806</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119720265</v>
+        <v>119719692</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1959,14 +1959,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>V bärtebo, V bärtebo, Vg</t>
+          <t>V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450347</v>
+        <v>450306</v>
       </c>
       <c r="R12" t="n">
-        <v>6437947</v>
+        <v>6437773</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119721569</v>
+        <v>119720296</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119720043</v>
+        <v>119720265</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,25 +2164,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450402</v>
+        <v>450347</v>
       </c>
       <c r="R14" t="n">
-        <v>6437806</v>
+        <v>6437947</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119720296</v>
+        <v>119721578</v>
       </c>
       <c r="B15" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2280,25 +2280,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,7 +2387,7 @@
         <v>119720721</v>
       </c>
       <c r="B16" t="n">
-        <v>89212</v>
+        <v>89229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73695510</v>
+        <v>119720721</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3B, Vg</t>
+          <t>V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450324.9279590423</v>
+        <v>450343</v>
       </c>
       <c r="R2" t="n">
-        <v>6437983.98998502</v>
+        <v>6438074</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,35 +774,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Sandbarrsvampar</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson, Louise Säf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73695514</v>
+        <v>73695503</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -837,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450341.9441011651</v>
+        <v>450291</v>
       </c>
       <c r="R3" t="n">
-        <v>6437903.919694675</v>
+        <v>6437794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +864,9 @@
           <t>2018-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,19 +898,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73695513</v>
+        <v>73695504</v>
       </c>
       <c r="B4" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -964,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450339.0292849456</v>
+        <v>450462</v>
       </c>
       <c r="R4" t="n">
-        <v>6437925.1106444</v>
+        <v>6437829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,19 +976,9 @@
           <t>2018-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,50 +1010,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73695816</v>
+        <v>73695507</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>3B, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450364.2252066481</v>
+        <v>450322</v>
       </c>
       <c r="R5" t="n">
-        <v>6438076.048431125</v>
+        <v>6437986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,27 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamlar fruktkroppar</t>
+          <t>2018-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,6 +1099,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1166,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf, Niklas Johansson</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1177,19 +1122,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73695503</v>
+        <v>73695512</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1212,7 +1152,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450290.7647731494</v>
+        <v>450334</v>
       </c>
       <c r="R6" t="n">
-        <v>6437794.023880904</v>
+        <v>6437969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,19 +1200,9 @@
           <t>2018-09-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,19 +1234,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73695507</v>
+        <v>73695513</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1339,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1354,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450321.7757379879</v>
+        <v>450339</v>
       </c>
       <c r="R7" t="n">
-        <v>6437986.144744318</v>
+        <v>6437925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,19 +1312,9 @@
           <t>2018-09-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,42 +1346,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73696930</v>
+        <v>73695514</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,16 +1384,17 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>3B, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450354.7797478172</v>
+        <v>450342</v>
       </c>
       <c r="R8" t="n">
-        <v>6437870.969768852</v>
+        <v>6437904</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,27 +1424,18 @@
           <t>2018-09-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-09-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1556,19 +1458,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73695512</v>
+        <v>79776777</v>
       </c>
       <c r="B9" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1591,25 +1488,20 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3B, Vg</t>
+          <t>Brandstorps distrikt, Hästebäcken, Hästhagen, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450333.7493150026</v>
+        <v>450334</v>
       </c>
       <c r="R9" t="n">
-        <v>6437969.071930905</v>
+        <v>6437912</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,22 +1528,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,14 +1552,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1677,25 +1568,20 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Sandbarrsvampar</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79776777</v>
+        <v>119719692</v>
       </c>
       <c r="B10" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1716,25 +1602,23 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brandstorps distrikt, Hästebäcken, Hästhagen, Habo kommun, Vg</t>
+          <t>V bärtebo, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450333.5665792754</v>
+        <v>450306</v>
       </c>
       <c r="R10" t="n">
-        <v>6437911.957191039</v>
+        <v>6437773</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1758,22 +1642,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,59 +1666,51 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson, Louise Säf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119720043</v>
+        <v>119720265</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1847,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450402</v>
+        <v>450347</v>
       </c>
       <c r="R11" t="n">
-        <v>6437806</v>
+        <v>6437947</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1882,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1892,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,15 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719692</v>
+        <v>73695510</v>
       </c>
       <c r="B12" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,40 +1807,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>V bärtebo, Vg</t>
+          <t>3B, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450306</v>
+        <v>450325</v>
       </c>
       <c r="R12" t="n">
-        <v>6437773</v>
+        <v>6437984</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1993,22 +1871,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2018-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2018-09-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,27 +1892,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Louise Säf</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119720296</v>
+        <v>73695816</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,40 +1919,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>V bärtebo, Vg</t>
+          <t>3B, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450306</v>
+        <v>450364</v>
       </c>
       <c r="R13" t="n">
-        <v>6437773</v>
+        <v>6438076</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2109,22 +1973,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamlar fruktkroppar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,34 +1992,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Louise Säf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Johan Staaf, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119720265</v>
+        <v>119720043</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2195,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450347</v>
+        <v>450402</v>
       </c>
       <c r="R14" t="n">
-        <v>6437947</v>
+        <v>6437806</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2230,7 +2087,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2240,7 +2097,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2268,19 +2125,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119721578</v>
+        <v>119721010</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2302,9 +2154,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>V bärtebo, Vg</t>
@@ -2346,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,7 +2205,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,7 +2214,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2377,44 +2225,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Louise Säf</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119720721</v>
+        <v>119720760</v>
       </c>
       <c r="B16" t="n">
-        <v>89229</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1593</v>
+        <v>4404</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,13 +2270,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450343</v>
+        <v>450306</v>
       </c>
       <c r="R16" t="n">
-        <v>6438074</v>
+        <v>6437773</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2462,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2503,12 +2346,7 @@
         <v>121357139</v>
       </c>
       <c r="B17" t="n">
-        <v>90748</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,6 +2447,439 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>73696930</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3B, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>450355</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6437871</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119720296</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>V bärtebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>450306</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6437773</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson, Louise Säf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>73695814</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3B, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>450450</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6437799</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tjäderhöna</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>73695813</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3B, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>450301</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6438188</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Orrhöna</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28832-2022 artfynd.xlsx
+++ b/artfynd/A 28832-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119720721</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695507</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695513</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79776777</t>
         </is>
       </c>
     </row>
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719692</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1793,6 +1843,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119720265</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695510</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695816</t>
         </is>
       </c>
     </row>
@@ -2122,6 +2187,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119720043</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119721010</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119720760</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2447,6 +2527,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121357139</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2555,6 +2640,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73696930</t>
         </is>
       </c>
     </row>
@@ -2668,6 +2758,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119720296</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2774,6 +2869,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695814</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2880,8 +2980,35 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>